--- a/Thesis_TSSP_NEW_M2_Results_5_Scenarios.xlsx
+++ b/Thesis_TSSP_NEW_M2_Results_5_Scenarios.xlsx
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>46.1620 sec</t>
+          <t>45.4240 sec</t>
         </is>
       </c>
     </row>

--- a/Thesis_TSSP_NEW_M2_Results_5_Scenarios.xlsx
+++ b/Thesis_TSSP_NEW_M2_Results_5_Scenarios.xlsx
@@ -478,17 +478,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 15:32</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4/5/2026 10:48</t>
+          <t>4/5/2026 10:49</t>
         </is>
       </c>
     </row>
@@ -500,32 +500,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4/5/2026 15:32</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4/5/2026 15:32</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/5/2026 12:03</t>
+          <t>4/5/2026 12:10</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4/5/2026 15:32</t>
+          <t>4/5/2026 06:52</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4/5/2026 11:47</t>
+          <t>4/5/2026 13:01</t>
         </is>
       </c>
     </row>
@@ -574,27 +574,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4/5/2026 08:53</t>
+          <t>4/5/2026 15:32</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4/5/2026 10:28</t>
+          <t>4/5/2026 13:10</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -611,32 +611,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4/5/2026 15:32</t>
+          <t>4/5/2026 13:29</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4/5/2026 15:32</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4/5/2026 10:33</t>
+          <t>4/5/2026 07:19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -663,17 +663,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4/5/2026 10:12</t>
+          <t>4/5/2026 13:13</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 07:56</t>
         </is>
       </c>
     </row>
@@ -685,32 +685,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4/5/2026 08:51</t>
+          <t>4/5/2026 15:31</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4/5/2026 14:28</t>
+          <t>4/5/2026 12:11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:08</t>
+          <t>4/5/2026 07:07</t>
         </is>
       </c>
     </row>
@@ -722,22 +722,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 13:24</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4/5/2026 12:01</t>
+          <t>4/5/2026 11:44</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4/5/2026 10:54</t>
+          <t>4/5/2026 11:04</t>
         </is>
       </c>
     </row>
@@ -764,27 +764,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4/5/2026 13:03</t>
+          <t>4/5/2026 10:47</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4/5/2026 15:01</t>
+          <t>4/5/2026 12:59</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 08:53</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4/5/2026 15:32</t>
+          <t>4/5/2026 15:31</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:26</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -833,32 +833,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4/5/2026 12:55</t>
+          <t>4/5/2026 11:38</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4/5/2026 15:29</t>
+          <t>4/5/2026 08:32</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4/5/2026 11:50</t>
+          <t>4/5/2026 11:52</t>
         </is>
       </c>
     </row>
@@ -870,27 +870,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 14:34</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4/5/2026 13:50</t>
+          <t>4/5/2026 15:17</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -907,32 +907,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4/5/2026 13:07</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4/5/2026 15:18</t>
+          <t>4/5/2026 14:23</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4/5/2026 15:14</t>
+          <t>4/5/2026 08:52</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4/5/2026 10:33</t>
+          <t>4/5/2026 15:25</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:27</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
     </row>
@@ -986,27 +986,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>4/5/2026 15:27</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Transport Cart 2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>4/5/2026 15:32</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Transport Cart 1</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:06</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4/5/2026 08:39</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1033,17 +1033,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:45</t>
+          <t>4/5/2026 09:43</t>
         </is>
       </c>
     </row>
@@ -1055,32 +1055,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:56</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4/5/2026 14:04</t>
+          <t>4/5/2026 11:37</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
     </row>
@@ -1097,27 +1097,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4/5/2026 15:27</t>
+          <t>4/5/2026 10:06</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:50</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
     </row>
@@ -1129,27 +1129,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4/5/2026 12:43</t>
+          <t>4/5/2026 08:48</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4/5/2026 15:32</t>
+          <t>4/5/2026 13:40</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1166,32 +1166,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4/5/2026 14:52</t>
+          <t>4/5/2026 08:44</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 15:28</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4/5/2026 11:38</t>
+          <t>4/5/2026 11:51</t>
         </is>
       </c>
     </row>
@@ -1208,17 +1208,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4/5/2026 14:56</t>
+          <t>4/5/2026 08:59</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:01</t>
+          <t>4/5/2026 15:00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>421.40 min</t>
+          <t>422.20 min</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>42.44 min</t>
+          <t>42.77 min</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>92.20 min</t>
+          <t>91.60 min</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>120.00 min</t>
+          <t>117.00 min</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>551599 / 31317</t>
+          <t>551603 / 31401</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>45.4240 sec</t>
+          <t>33.5260 sec</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.8031 %</t>
+          <t>1.8686 %</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>46.10 min | 120.00 min</t>
+          <t>47.05 min | 117.00 min</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>41.14 min | 86.00 min</t>
+          <t>40.05 min | 86.00 min</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>38.95 min | 83.00 min</t>
+          <t>40.81 min | 83.00 min</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>42.52 min | 82.00 min</t>
+          <t>43.19 min | 82.00 min</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>43.48 min | 90.00 min</t>
+          <t>42.76 min | 90.00 min</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>16.31</v>
+        <v>18.61</v>
       </c>
     </row>
     <row r="36">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>11.65</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="37">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>9.32</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="38">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>11.65</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="39">
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4.54</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="40">
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3.18</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="41">
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.82</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="42">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31.59</v>
+        <v>22.52</v>
       </c>
     </row>
     <row r="43">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>36.11</v>
+        <v>36.04</v>
       </c>
     </row>
     <row r="44">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>27.08</v>
+        <v>36.04</v>
       </c>
     </row>
   </sheetData>
@@ -1845,35 +1845,35 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/5/2026 09:57</t>
+          <t>4/5/2026 09:54</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4/5/2026 09:59</t>
+          <t>4/5/2026 09:56</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4/5/2026 10:09</t>
+          <t>4/5/2026 10:06</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4/5/2026 11:13</t>
+          <t>4/5/2026 11:10</t>
         </is>
       </c>
       <c r="L3" t="n">
         <v>10</v>
       </c>
       <c r="M3" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="N3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -2012,25 +2012,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -2038,22 +2038,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>4/5/2026 09:13</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>4/5/2026 09:14</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:15</t>
-        </is>
-      </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -2072,25 +2072,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:27</t>
+          <t>4/5/2026 07:29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:36</t>
+          <t>4/5/2026 07:38</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:43</t>
+          <t>4/5/2026 07:45</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:44</t>
+          <t>4/5/2026 07:46</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -2098,22 +2098,22 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 07:56</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4/5/2026 08:02</t>
+          <t>4/5/2026 08:12</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="N7" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -2145,35 +2145,35 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:03</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:05</t>
+          <t>4/5/2026 07:06</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:08</t>
+          <t>4/5/2026 07:07</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -2218,22 +2218,22 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4/5/2026 10:54</t>
+          <t>4/5/2026 11:04</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4/5/2026 11:23</t>
+          <t>4/5/2026 11:33</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="N9" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -2252,48 +2252,48 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4/5/2026 08:27</t>
+          <t>4/5/2026 08:37</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4/5/2026 08:38</t>
+          <t>4/5/2026 08:48</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4/5/2026 08:43</t>
+          <t>4/5/2026 08:51</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 08:53</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4/5/2026 08:55</t>
+          <t>4/5/2026 08:53</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -2445,16 +2445,16 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:24</t>
+          <t>4/5/2026 11:25</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:27</t>
+          <t>4/5/2026 11:28</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>35</v>
@@ -2492,48 +2492,48 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 08:49</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:54</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>9</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:03</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:05</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>7</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>4/5/2026 08:59</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:01</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>5</v>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:43</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N14" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
@@ -2578,22 +2578,22 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:27</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:29</t>
+          <t>4/5/2026 06:23</t>
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
         <v>7</v>
       </c>
-      <c r="M15" t="n">
-        <v>13</v>
-      </c>
       <c r="N15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -2612,48 +2612,48 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4/5/2026 08:25</t>
+          <t>4/5/2026 08:35</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4/5/2026 08:37</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4/5/2026 08:37</t>
+          <t>4/5/2026 08:54</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4/5/2026 08:39</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4/5/2026 08:39</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M16" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -2685,35 +2685,35 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:45</t>
+          <t>4/5/2026 09:43</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:54</t>
+          <t>4/5/2026 09:52</t>
         </is>
       </c>
       <c r="L17" t="n">
         <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N17" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -2732,48 +2732,48 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:45</t>
+          <t>4/5/2026 09:41</t>
         </is>
       </c>
       <c r="L18" t="n">
         <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="N18" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -2805,35 +2805,35 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:40</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:50</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>4/5/2026 10:10</t>
+          <t>4/5/2026 10:04</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="N19" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2912,48 +2912,48 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:42</t>
+          <t>4/5/2026 08:32</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 08:46</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 08:51</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 08:52</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>4/5/2026 09:50</t>
+          <t>4/5/2026 09:25</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="N21" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -2972,48 +2972,48 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4/5/2026 08:57</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M22" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -3058,22 +3058,22 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4/5/2026 10:48</t>
+          <t>4/5/2026 10:49</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4/5/2026 11:18</t>
+          <t>4/5/2026 11:19</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -3165,35 +3165,35 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4/5/2026 12:57</t>
+          <t>4/5/2026 12:58</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4/5/2026 13:00</t>
+          <t>4/5/2026 13:01</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>4/5/2026 13:00</t>
+          <t>4/5/2026 13:01</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>4/5/2026 13:07</t>
+          <t>4/5/2026 13:08</t>
         </is>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -3285,35 +3285,35 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>4/5/2026 09:13</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>4/5/2026 09:14</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:15</t>
-        </is>
-      </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -3358,22 +3358,22 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 07:56</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>4/5/2026 08:02</t>
+          <t>4/5/2026 08:12</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M28" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="N28" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
@@ -3392,25 +3392,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4/5/2026 06:49</t>
+          <t>4/5/2026 06:48</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4/5/2026 07:04</t>
+          <t>4/5/2026 07:03</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4/5/2026 07:04</t>
+          <t>4/5/2026 07:03</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4/5/2026 07:06</t>
+          <t>4/5/2026 07:05</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -3418,22 +3418,22 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4/5/2026 07:08</t>
+          <t>4/5/2026 07:07</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="L29" t="n">
         <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -3465,35 +3465,35 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4/5/2026 12:20</t>
+          <t>4/5/2026 12:13</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4/5/2026 12:22</t>
+          <t>4/5/2026 12:15</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>4/5/2026 12:29</t>
+          <t>4/5/2026 12:15</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>4/5/2026 12:53</t>
+          <t>4/5/2026 12:39</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="N30" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -3525,35 +3525,35 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4/5/2026 11:06</t>
+          <t>4/5/2026 10:59</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4/5/2026 11:08</t>
+          <t>4/5/2026 11:01</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4/5/2026 11:18</t>
+          <t>4/5/2026 11:01</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>4/5/2026 11:30</t>
+          <t>4/5/2026 11:13</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="N31" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3572,48 +3572,48 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:04</t>
+          <t>4/5/2026 11:05</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:08</t>
+          <t>4/5/2026 11:09</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:08</t>
+          <t>4/5/2026 11:11</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:10</t>
+          <t>4/5/2026 11:13</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:11</t>
+          <t>4/5/2026 11:13</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:32</t>
+          <t>4/5/2026 11:34</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -3692,25 +3692,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:34</t>
+          <t>4/5/2026 08:32</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:44</t>
+          <t>4/5/2026 08:42</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:51</t>
+          <t>4/5/2026 08:49</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:52</t>
+          <t>4/5/2026 08:50</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M34" t="n">
         <v>63</v>
@@ -3765,35 +3765,35 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4/5/2026 08:57</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4/5/2026 08:59</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="L35" t="n">
         <v>10</v>
       </c>
       <c r="M35" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="N35" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36">
@@ -3838,22 +3838,22 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>4/5/2026 06:27</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>4/5/2026 06:29</t>
+          <t>4/5/2026 06:23</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="N36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3932,48 +3932,48 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:28</t>
+          <t>4/5/2026 09:24</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:36</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:45</t>
+          <t>4/5/2026 09:43</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:54</t>
+          <t>4/5/2026 09:52</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M38" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N38" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
@@ -3992,48 +3992,48 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>4/5/2026 09:45</t>
+          <t>4/5/2026 09:41</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M39" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="N39" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
@@ -4052,48 +4052,48 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:32</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:40</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:50</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>4/5/2026 10:10</t>
+          <t>4/5/2026 10:04</t>
         </is>
       </c>
       <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>48</v>
+      </c>
+      <c r="N40" t="n">
         <v>10</v>
-      </c>
-      <c r="M40" t="n">
-        <v>54</v>
-      </c>
-      <c r="N40" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="41">
@@ -4198,22 +4198,22 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>4/5/2026 11:59</t>
+          <t>4/5/2026 11:51</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>4/5/2026 12:29</t>
+          <t>4/5/2026 12:21</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="N42" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -4232,48 +4232,48 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M43" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44">
@@ -4472,25 +4472,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4/5/2026 12:50</t>
+          <t>4/5/2026 12:51</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>4/5/2026 12:54</t>
+          <t>4/5/2026 12:55</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>4/5/2026 12:54</t>
+          <t>4/5/2026 12:55</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>4/5/2026 12:56</t>
+          <t>4/5/2026 12:57</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>34</v>
@@ -4532,48 +4532,48 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
+          <t>4/5/2026 09:12</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:13</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>4/5/2026 09:14</t>
         </is>
       </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:14</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:15</t>
-        </is>
-      </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -4618,22 +4618,22 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 07:56</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>4/5/2026 08:02</t>
+          <t>4/5/2026 08:12</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M49" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="N49" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50">
@@ -4678,22 +4678,22 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>4/5/2026 07:08</t>
+          <t>4/5/2026 07:07</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -4725,35 +4725,35 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>4/5/2026 10:46</t>
+          <t>4/5/2026 10:53</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4/5/2026 10:48</t>
+          <t>4/5/2026 10:55</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>4/5/2026 10:49</t>
+          <t>4/5/2026 11:02</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>4/5/2026 11:18</t>
+          <t>4/5/2026 11:31</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M51" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="N51" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52">
@@ -4832,48 +4832,48 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4/5/2026 11:04</t>
+          <t>4/5/2026 11:14</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>4/5/2026 11:08</t>
+          <t>4/5/2026 11:18</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>4/5/2026 11:08</t>
+          <t>4/5/2026 11:25</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4/5/2026 11:10</t>
+          <t>4/5/2026 11:27</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>4/5/2026 11:18</t>
+          <t>4/5/2026 11:32</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>4/5/2026 11:39</t>
+          <t>4/5/2026 11:53</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M53" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="N53" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54">
@@ -4892,48 +4892,48 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4/5/2026 11:41</t>
+          <t>4/5/2026 11:42</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>4/5/2026 11:48</t>
+          <t>4/5/2026 11:49</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>4/5/2026 11:55</t>
+          <t>4/5/2026 11:53</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4/5/2026 11:56</t>
+          <t>4/5/2026 11:54</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>4/5/2026 12:06</t>
+          <t>4/5/2026 11:54</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>4/5/2026 12:12</t>
+          <t>4/5/2026 12:00</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="N54" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -5085,35 +5085,35 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
+          <t>4/5/2026 06:19</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
           <t>4/5/2026 06:21</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>4/5/2026 06:21</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>4/5/2026 06:23</t>
         </is>
       </c>
-      <c r="I57" t="n">
-        <v>3</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>4/5/2026 06:27</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>4/5/2026 06:29</t>
-        </is>
-      </c>
       <c r="L57" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="N57" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -5205,35 +5205,35 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
+          <t>4/5/2026 09:31</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
           <t>4/5/2026 09:33</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:35</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:45</t>
+          <t>4/5/2026 09:43</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:54</t>
+          <t>4/5/2026 09:52</t>
         </is>
       </c>
       <c r="L59" t="n">
         <v>10</v>
       </c>
       <c r="M59" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N59" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60">
@@ -5252,48 +5252,48 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:26</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:28</t>
+          <t>4/5/2026 09:24</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:45</t>
+          <t>4/5/2026 09:41</t>
         </is>
       </c>
       <c r="L60" t="n">
         <v>9</v>
       </c>
       <c r="M60" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="N60" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61">
@@ -5312,48 +5312,48 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>4/5/2026 09:42</t>
+          <t>4/5/2026 09:41</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>4/5/2026 09:47</t>
+          <t>4/5/2026 09:41</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>4/5/2026 09:50</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>4/5/2026 09:50</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>4/5/2026 10:10</t>
+          <t>4/5/2026 10:04</t>
         </is>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="N61" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
@@ -5398,22 +5398,22 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>4/5/2026 12:10</t>
+          <t>4/5/2026 12:16</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>4/5/2026 12:38</t>
+          <t>4/5/2026 12:44</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M62" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
@@ -5458,22 +5458,22 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>4/5/2026 11:41</t>
+          <t>4/5/2026 11:51</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>4/5/2026 12:06</t>
+          <t>4/5/2026 12:16</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M63" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64">
@@ -5492,48 +5492,48 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:24</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:27</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M64" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65">
@@ -5792,25 +5792,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -5818,22 +5818,22 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t>4/5/2026 09:13</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t>4/5/2026 09:14</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:15</t>
-        </is>
-      </c>
       <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>6</v>
+      </c>
+      <c r="N69" t="n">
         <v>2</v>
-      </c>
-      <c r="M69" t="n">
-        <v>7</v>
-      </c>
-      <c r="N69" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -5852,25 +5852,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>4/5/2026 07:27</t>
+          <t>4/5/2026 07:29</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>4/5/2026 07:36</t>
+          <t>4/5/2026 07:38</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>4/5/2026 07:43</t>
+          <t>4/5/2026 07:45</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>4/5/2026 07:44</t>
+          <t>4/5/2026 07:46</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -5878,22 +5878,22 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 07:56</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>4/5/2026 08:02</t>
+          <t>4/5/2026 08:12</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M70" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="N70" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="71">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>4/5/2026 07:08</t>
+          <t>4/5/2026 07:07</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M71" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N71" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
@@ -6032,48 +6032,48 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>4/5/2026 08:29</t>
+          <t>4/5/2026 08:27</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>4/5/2026 08:35</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
           <t>4/5/2026 08:37</t>
         </is>
       </c>
-      <c r="F73" t="n">
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>4/5/2026 08:40</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
         <v>2</v>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>4/5/2026 08:44</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>4/5/2026 08:47</t>
-        </is>
-      </c>
-      <c r="I73" t="n">
-        <v>7</v>
-      </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 08:50</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>4/5/2026 09:26</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M73" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="N73" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74">
@@ -6105,16 +6105,16 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>4/5/2026 11:08</t>
+          <t>4/5/2026 11:09</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>4/5/2026 11:10</t>
+          <t>4/5/2026 11:11</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
         <v>28</v>
@@ -6358,22 +6358,22 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>4/5/2026 06:27</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>4/5/2026 06:29</t>
+          <t>4/5/2026 06:23</t>
         </is>
       </c>
       <c r="L78" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" t="n">
         <v>7</v>
       </c>
-      <c r="M78" t="n">
-        <v>13</v>
-      </c>
       <c r="N78" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -6452,48 +6452,48 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:28</t>
+          <t>4/5/2026 09:25</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
+          <t>4/5/2026 09:31</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
           <t>4/5/2026 09:33</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:35</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:45</t>
+          <t>4/5/2026 09:43</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:54</t>
+          <t>4/5/2026 09:52</t>
         </is>
       </c>
       <c r="L80" t="n">
         <v>10</v>
       </c>
       <c r="M80" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N80" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81">
@@ -6525,35 +6525,35 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:24</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>4/5/2026 09:45</t>
+          <t>4/5/2026 09:41</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M81" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="N81" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82">
@@ -6585,35 +6585,35 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:38</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>4/5/2026 09:57</t>
+          <t>4/5/2026 10:04</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M82" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="N82" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83">
@@ -6752,48 +6752,48 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="L85" t="n">
         <v>3</v>
       </c>
       <c r="M85" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="N85" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86">
@@ -6872,25 +6872,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>4/5/2026 11:34</t>
+          <t>4/5/2026 11:35</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>4/5/2026 12:05</t>
+          <t>4/5/2026 12:06</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>4/5/2026 12:05</t>
+          <t>4/5/2026 12:06</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>4/5/2026 12:07</t>
+          <t>4/5/2026 12:08</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -6898,22 +6898,22 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>4/5/2026 12:07</t>
+          <t>4/5/2026 12:10</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>4/5/2026 12:53</t>
+          <t>4/5/2026 12:56</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M87" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
@@ -6992,48 +6992,48 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 08:53</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:01</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M89" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="N89" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90">
@@ -7078,22 +7078,22 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t>4/5/2026 09:13</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t>4/5/2026 09:14</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:15</t>
-        </is>
-      </c>
       <c r="L90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M90" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -7112,48 +7112,48 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>4/5/2026 07:21</t>
+          <t>4/5/2026 07:29</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:38</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>4/5/2026 07:36</t>
+          <t>4/5/2026 07:45</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>4/5/2026 07:37</t>
+          <t>4/5/2026 07:46</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 07:56</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>4/5/2026 08:02</t>
+          <t>4/5/2026 08:12</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M91" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="N91" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="92">
@@ -7172,48 +7172,48 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>4/5/2026 06:48</t>
+          <t>4/5/2026 06:50</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>4/5/2026 06:58</t>
+          <t>4/5/2026 07:00</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>4/5/2026 07:00</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>4/5/2026 07:02</t>
+          <t>4/5/2026 07:06</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>4/5/2026 07:08</t>
+          <t>4/5/2026 07:07</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N92" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93">
@@ -7292,48 +7292,48 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>4/5/2026 08:27</t>
+          <t>4/5/2026 08:32</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>4/5/2026 08:36</t>
+          <t>4/5/2026 08:41</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:44</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>4/5/2026 08:42</t>
+          <t>4/5/2026 08:46</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>4/5/2026 08:52</t>
+          <t>4/5/2026 08:53</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M94" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N94" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95">
@@ -7532,48 +7532,48 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:49</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>4/5/2026 08:50</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>4/5/2026 08:52</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>4/5/2026 08:55</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:43</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M98" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="N98" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="99">
@@ -7605,35 +7605,35 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>4/5/2026 06:20</t>
+          <t>4/5/2026 06:19</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>4/5/2026 06:22</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>4/5/2026 06:27</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>4/5/2026 06:29</t>
+          <t>4/5/2026 06:23</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="N99" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -7738,22 +7738,22 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:45</t>
+          <t>4/5/2026 09:43</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:54</t>
+          <t>4/5/2026 09:52</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M101" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N101" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102">
@@ -7772,48 +7772,48 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
+          <t>4/5/2026 09:24</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
           <t>4/5/2026 09:26</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:28</t>
-        </is>
-      </c>
       <c r="I102" t="n">
+        <v>3</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:33</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:41</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
         <v>7</v>
       </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:37</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:45</t>
-        </is>
-      </c>
-      <c r="L102" t="n">
-        <v>9</v>
-      </c>
       <c r="M102" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="N102" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103">
@@ -7832,48 +7832,48 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4/5/2026 09:40</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>4/5/2026 09:50</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>4/5/2026 10:10</t>
+          <t>4/5/2026 10:04</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="N103" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104">
@@ -7952,48 +7952,48 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4/5/2026 08:42</t>
+          <t>4/5/2026 08:32</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4/5/2026 08:57</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 08:49</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 08:49</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>4/5/2026 09:49</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="N105" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -8012,48 +8012,48 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 09:00</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M106" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="N106" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
